--- a/naver-place-crawler/results_nail/원주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/원주_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>레푸스 원주점</t>
+          <t>뉴닝네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>refuss-wonju@naver.com</t>
+          <t>maybe0570@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1410-0050</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 51 3층 321호</t>
+          <t>강원 원주시 단구로 109 , 102호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Qenwxj/chat</t>
+          <t>http://pf.kakao.com/_xaDxbdG</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -602,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4soe3</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -617,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1193</v>
+        <v>527</v>
       </c>
       <c r="Q2" t="n">
-        <v>994</v>
+        <v>113</v>
       </c>
       <c r="R2" t="n">
-        <v>2187</v>
+        <v>640</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1178461799</t>
+          <t>1064876657</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1178461799</t>
+          <t>https://m.place.naver.com/place/1064876657</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -654,34 +662,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴닝네일</t>
+          <t>봄봄네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>maybe0570@naver.com</t>
+          <t>bjy5623@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1410-0050</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 단구로 109</t>
+          <t>강원 원주시 능라동길 61 정한타워 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xaDxbdG</t>
+          <t>https://www.instagram.com/bomnail_studio</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -696,17 +700,13 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4soe3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>523</v>
+        <v>1350</v>
       </c>
       <c r="Q3" t="n">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="R3" t="n">
-        <v>636</v>
+        <v>1386</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1064876657</t>
+          <t>1899644051</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1064876657</t>
+          <t>https://m.place.naver.com/place/1899644051</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -752,12 +752,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>봄봄네일&amp;뷰티</t>
+          <t>레푸스 원주점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bjy5623@naver.com</t>
+          <t>refuss-wonju@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -765,17 +765,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 61 정한타워 4층</t>
+          <t>강원 원주시 능라동길 51 3층 321호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bomnail_studio</t>
+          <t>http://pf.kakao.com/_Qenwxj/chat</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -796,7 +796,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1335</v>
+        <v>1194</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="R4" t="n">
-        <v>1371</v>
+        <v>2194</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1899644051</t>
+          <t>1178461799</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899644051</t>
+          <t>https://m.place.naver.com/place/1178461799</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -842,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일몬스터앤뷰티</t>
+          <t>다니니네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rr4925@naver.com</t>
+          <t>jihoomom0906@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1417-0503</t>
+          <t>0507-1418-8813</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 원주시 천사로 14 1층</t>
+          <t>강원 원주시 황소마을길 13-1 1층 102호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmonster._</t>
+          <t>https://www.instagram.com/danini_nail/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4230x</t>
+          <t>https://talk.naver.com/ct/w5uzqt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>554</v>
+        <v>233</v>
       </c>
       <c r="Q5" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="R5" t="n">
-        <v>687</v>
+        <v>346</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1266892779</t>
+          <t>1743962217</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266892779</t>
+          <t>https://m.place.naver.com/place/1743962217</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>다니니네일</t>
+          <t>네일봄</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jihoomom0906@naver.com</t>
+          <t>llo__ob@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1418-8813</t>
+          <t>0507-1322-9731</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 원주시 황소마을길 13-1 1층 102호</t>
+          <t>강원 원주시 만대공원길 50 107호 네일봄</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/danini_nail/</t>
+          <t>https://blog.naver.com/llo__ob</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uzqt</t>
+          <t>https://talk.naver.com/ct/w4nebs</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="Q6" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="R6" t="n">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1743962217</t>
+          <t>1017730079</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743962217</t>
+          <t>https://m.place.naver.com/place/1017730079</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일봄</t>
+          <t>원멜리 네일앤뷰티</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>llo__ob@naver.com</t>
+          <t>wonmeli_nail@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1322-9731</t>
+          <t>0507-1467-5661</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 원주시 만대공원길 50 107호 네일봄</t>
+          <t>강원 원주시 이화4길 55 1층 101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/llo__ob</t>
+          <t>https://www.instagram.com/wonmeli_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4nebs</t>
+          <t>https://talk.naver.com/ct/w5ixs9</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="Q7" t="n">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1017730079</t>
+          <t>1804062627</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1017730079</t>
+          <t>https://m.place.naver.com/place/1804062627</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1136,34 +1136,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>새론네일</t>
+          <t>네일탐나</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jscleancompany@naver.com</t>
+          <t>gjguswjd04@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1486-9982</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 구곡길 29 1층</t>
+          <t>강원 원주시 치악고교길 28 1층 네일탐나</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_KenyG</t>
+          <t>https://www.instagram.com/__.nail_tamna</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1183,7 +1179,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vlez</t>
+          <t>https://talk.naver.com/ct/w4c5oc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1197,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1369131080</t>
+          <t>1611111219</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369131080</t>
+          <t>https://m.place.naver.com/place/1611111219</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1234,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>원멜리 네일앤뷰티</t>
+          <t>글래드 네일 원주점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wonmeli_nail@naver.com</t>
+          <t>kdm7875@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1467-5661</t>
+          <t>0507-1310-0165</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 이화4길 55 1층 101호</t>
+          <t>강원 원주시 이화2길 23 1층 글래드네일 원주점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wonmeli_nail</t>
+          <t>https://www.instagram.com/glad_nail_studio</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1281,7 +1277,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ixs9</t>
+          <t>https://talk.naver.com/ct/w4qu8o</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1295,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>241</v>
+        <v>1026</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>256</v>
+        <v>1040</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1804062627</t>
+          <t>1333012511</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1804062627</t>
+          <t>https://m.place.naver.com/place/1333012511</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1332,29 +1328,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>예삐네일</t>
+          <t>플루피네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hott0116@naver.com</t>
+          <t>do-ob123@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1386-8456</t>
+          <t>0507-1468-0679</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 51 319호</t>
+          <t>강원 원주시 섬밭들1길 2-5 1층 뷰티에스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeppi_nail</t>
+          <t>https://www.instagram.com/fluffy_nail___?igsh=dXZpZGVnczNhM2oz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1379,7 +1375,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48fji</t>
+          <t>https://talk.naver.com/ct/w5vldj</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1393,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,17 +1404,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1771502408</t>
+          <t>1675165272</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1771502408</t>
+          <t>https://m.place.naver.com/place/1675165272</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1430,25 +1426,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일탐나</t>
+          <t>위시네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>yujinlub@naver.com</t>
+          <t>enoctobre-@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1309-5808</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>강원 원주시 치악고교길 28 1층 네일탐나</t>
+          <t>강원 원주시 황소마을길 28-1 1층 103호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__.nail_tamna</t>
+          <t>https://open.kakao.com/o/sQL80ihi</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4c5oc</t>
+          <t>https://talk.naver.com/ct/whzlx0r</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1487,32 +1487,126 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>49</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2080857031</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2080857031</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>리브네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ljgda0118@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1315-9765</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>강원 원주시 진광길 47 1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rivnail_?igsh=MWNvczJucm5xdDhr</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>99</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1611111219</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1611111219</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="R12" t="n">
+        <v>16</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2054372763</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2054372763</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/원주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/원주_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>뉴닝네일</t>
+          <t>다니니네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>maybe0570@naver.com</t>
+          <t>jihoomom0906@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1410-0050</t>
+          <t>0507-1418-8813</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 원주시 단구로 109 , 102호</t>
+          <t>강원 원주시 황소마을길 13-1 1층 102호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xaDxbdG</t>
+          <t>https://www.instagram.com/danini_nail/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4soe3</t>
+          <t>https://talk.naver.com/ct/w5uzqt</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>527</v>
+        <v>234</v>
       </c>
       <c r="Q2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R2" t="n">
-        <v>640</v>
+        <v>348</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1064876657</t>
+          <t>1743962217</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1064876657</t>
+          <t>https://m.place.naver.com/place/1743962217</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,30 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>봄봄네일&amp;뷰티</t>
+          <t>뉴닝네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bjy5623@naver.com</t>
+          <t>maybe0570@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1410-0050</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 61 정한타워 4층</t>
+          <t>강원 원주시 단구로 109 , 102호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bomnail_studio</t>
+          <t>http://pf.kakao.com/_xaDxbdG</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -700,13 +704,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4soe3</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1350</v>
+        <v>527</v>
       </c>
       <c r="Q3" t="n">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="R3" t="n">
-        <v>1386</v>
+        <v>640</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1899644051</t>
+          <t>1064876657</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1899644051</t>
+          <t>https://m.place.naver.com/place/1064876657</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,12 +760,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>레푸스 원주점</t>
+          <t>봄봄네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>refuss-wonju@naver.com</t>
+          <t>bjy5623@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -765,17 +773,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 51 3층 321호</t>
+          <t>강원 원주시 능라동길 61 정한타워 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Qenwxj/chat</t>
+          <t>https://www.instagram.com/bomnail_studio</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -796,7 +804,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -805,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1194</v>
+        <v>1358</v>
       </c>
       <c r="Q4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="R4" t="n">
-        <v>2194</v>
+        <v>1394</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1178461799</t>
+          <t>1899644051</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1178461799</t>
+          <t>https://m.place.naver.com/place/1899644051</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -842,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>다니니네일</t>
+          <t>LUDA 네일&amp;브로우</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jihoomom0906@naver.com</t>
+          <t>dkfma801@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1418-8813</t>
+          <t>0507-1353-9235</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 원주시 황소마을길 13-1 1층 102호</t>
+          <t>강원 원주시 서원대로 434 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/danini_nail/</t>
+          <t>http://instagram.com/luda3nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -889,12 +897,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uzqt</t>
+          <t>https://talk.naver.com/ct/w4xotr</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>233</v>
+        <v>634</v>
       </c>
       <c r="Q5" t="n">
-        <v>113</v>
+        <v>208</v>
       </c>
       <c r="R5" t="n">
-        <v>346</v>
+        <v>842</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +926,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1743962217</t>
+          <t>1238546921</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743962217</t>
+          <t>https://m.place.naver.com/place/1238546921</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,34 +948,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일봄</t>
+          <t>레푸스 원주점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>llo__ob@naver.com</t>
+          <t>refuss-wonju@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1322-9731</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 원주시 만대공원길 50 107호 네일봄</t>
+          <t>강원 원주시 능라동길 51 3층 321호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/llo__ob</t>
+          <t>http://pf.kakao.com/_Qenwxj/chat</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,22 +981,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4nebs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>201</v>
+        <v>1194</v>
       </c>
       <c r="Q6" t="n">
-        <v>105</v>
+        <v>1000</v>
       </c>
       <c r="R6" t="n">
-        <v>306</v>
+        <v>2194</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1017730079</t>
+          <t>1178461799</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1017730079</t>
+          <t>https://m.place.naver.com/place/1178461799</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1038,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원멜리 네일앤뷰티</t>
+          <t>원주네일밸류</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wonmeli_nail@naver.com</t>
+          <t>rlatndus9800@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1467-5661</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 원주시 이화4길 55 1층 101호</t>
+          <t>강원 원주시 서원대로 408 602호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wonmeli_nail</t>
+          <t>https://www.instagram.com/nailvalue_salon_official</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1085,12 +1081,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ixs9</t>
+          <t>https://talk.naver.com/ct/w4ejib</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1804062627</t>
+          <t>1791919601</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1804062627</t>
+          <t>https://m.place.naver.com/place/1791919601</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1136,30 +1132,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일탐나</t>
+          <t>새론네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gjguswjd04@naver.com</t>
+          <t>jscleancompany@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1486-9982</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 치악고교길 28 1층 네일탐나</t>
+          <t>강원 원주시 구곡길 29 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__.nail_tamna</t>
+          <t>http://pf.kakao.com/_KenyG</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4c5oc</t>
+          <t>https://talk.naver.com/ct/w5vlez</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1611111219</t>
+          <t>1369131080</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611111219</t>
+          <t>https://m.place.naver.com/place/1369131080</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1230,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>글래드 네일 원주점</t>
+          <t>원멜리 네일앤뷰티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kdm7875@naver.com</t>
+          <t>wonmeli_nail@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1310-0165</t>
+          <t>0507-1467-5661</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 이화2길 23 1층 글래드네일 원주점</t>
+          <t>강원 원주시 이화4길 55 1층 101호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/glad_nail_studio</t>
+          <t>https://www.instagram.com/wonmeli_nail</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4qu8o</t>
+          <t>https://talk.naver.com/ct/w5ixs9</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1026</v>
+        <v>243</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
-        <v>1040</v>
+        <v>258</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1333012511</t>
+          <t>1804062627</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1333012511</t>
+          <t>https://m.place.naver.com/place/1804062627</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>플루피네일</t>
+          <t>예삐네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>do-ob123@naver.com</t>
+          <t>hott0116@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1468-0679</t>
+          <t>0507-1386-8456</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>강원 원주시 섬밭들1길 2-5 1층 뷰티에스</t>
+          <t>강원 원주시 능라동길 51 319호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fluffy_nail___?igsh=dXZpZGVnczNhM2oz</t>
+          <t>https://www.instagram.com/yeppi_nail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vldj</t>
+          <t>https://talk.naver.com/ct/w48fji</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,17 +1404,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1675165272</t>
+          <t>1771502408</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1675165272</t>
+          <t>https://m.place.naver.com/place/1771502408</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1426,29 +1426,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>위시네일</t>
+          <t>네일탐나</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>enoctobre-@naver.com</t>
+          <t>solo-traveller@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1309-5808</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>강원 원주시 황소마을길 28-1 1층 103호</t>
+          <t>강원 원주시 치악고교길 28 1층 네일탐나</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sQL80ihi</t>
+          <t>https://www.instagram.com/__.nail_tamna</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1473,7 +1469,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/whzlx0r</t>
+          <t>https://talk.naver.com/ct/w4c5oc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1487,13 +1483,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1502,111 +1498,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2080857031</t>
+          <t>1611111219</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080857031</t>
+          <t>https://m.place.naver.com/place/1611111219</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>리브네일</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ljgda0118@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1315-9765</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>강원 원주시 진광길 47 1층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/rivnail_?igsh=MWNvczJucm5xdDhr</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>16</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2054372763</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2054372763</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/원주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/원주_네일샵.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jihoomom0906@naver.com</t>
+          <t>ju_youngkim@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="Q6" t="n">
         <v>1000</v>
       </c>
       <c r="R6" t="n">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,30 +1038,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원주네일밸류</t>
+          <t>원멜리 네일앤뷰티</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rlatndus9800@naver.com</t>
+          <t>wonmeli_nail@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1467-5661</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>강원 원주시 서원대로 408 602호</t>
+          <t>강원 원주시 이화4길 55 1층 101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailvalue_salon_official</t>
+          <t>https://www.instagram.com/wonmeli_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1081,12 +1085,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ejib</t>
+          <t>https://talk.naver.com/ct/w5ixs9</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="Q7" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1114,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1791919601</t>
+          <t>1804062627</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1791919601</t>
+          <t>https://m.place.naver.com/place/1804062627</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,34 +1136,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>새론네일</t>
+          <t>네일탐나</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jscleancompany@naver.com</t>
+          <t>solo-traveller@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1486-9982</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 원주시 구곡길 29 1층</t>
+          <t>강원 원주시 치악고교길 28 1층 네일탐나</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_KenyG</t>
+          <t>https://www.instagram.com/__.nail_tamna</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vlez</t>
+          <t>https://talk.naver.com/ct/w4c5oc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1369131080</t>
+          <t>1611111219</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369131080</t>
+          <t>https://m.place.naver.com/place/1611111219</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1230,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>원멜리 네일앤뷰티</t>
+          <t>글래드 네일 원주점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wonmeli_nail@naver.com</t>
+          <t>kdm7875@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1467-5661</t>
+          <t>0507-1310-0165</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 원주시 이화4길 55 1층 101호</t>
+          <t>강원 원주시 이화2길 23 1층 글래드네일 원주점</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wonmeli_nail</t>
+          <t>https://www.instagram.com/glad_nail_studio</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ixs9</t>
+          <t>https://talk.naver.com/ct/w4qu8o</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>243</v>
+        <v>1026</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R9" t="n">
-        <v>258</v>
+        <v>1040</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1804062627</t>
+          <t>1333012511</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1804062627</t>
+          <t>https://m.place.naver.com/place/1333012511</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1328,29 +1328,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>예삐네일</t>
+          <t>플루피네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hott0116@naver.com</t>
+          <t>do-ob123@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1386-8456</t>
+          <t>0507-1468-0679</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>강원 원주시 능라동길 51 319호</t>
+          <t>강원 원주시 섬밭들1길 2-5 1층 뷰티에스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeppi_nail</t>
+          <t>https://www.instagram.com/fluffy_nail___?igsh=dXZpZGVnczNhM2oz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48fji</t>
+          <t>https://talk.naver.com/ct/w5vldj</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1771502408</t>
+          <t>1675165272</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1771502408</t>
+          <t>https://m.place.naver.com/place/1675165272</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1426,25 +1426,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일탐나</t>
+          <t>위시네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>solo-traveller@naver.com</t>
+          <t>enoctobre-@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1309-5808</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>강원 원주시 치악고교길 28 1층 네일탐나</t>
+          <t>강원 원주시 황소마을길 28-1 1층 103호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__.nail_tamna</t>
+          <t>https://open.kakao.com/o/sQL80ihi</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1469,7 +1473,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4c5oc</t>
+          <t>https://talk.naver.com/ct/whzlx0r</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1483,13 +1487,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1498,12 +1502,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1611111219</t>
+          <t>2080857031</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1611111219</t>
+          <t>https://m.place.naver.com/place/2080857031</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_nail/원주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/원주_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V148"/>
+  <dimension ref="A1:V235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14038,6 +14038,7904 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>네일드블랑</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 중앙시장길 2-44 1층 네일드블랑</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>http://naild.7x7.kr</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>30</v>
+      </c>
+      <c r="R149" t="n">
+        <v>56</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>1578690894</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1578690894</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>쏘온즈네일</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0507-1409-6078</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 양지로 70 서영에비뉴파크3차 108호</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/ssooooons_nail/</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>8</v>
+      </c>
+      <c r="R150" t="n">
+        <v>23</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>401270224</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/401270224</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>블랑쉬네일</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>0507-1389-3139</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 만대로 180 1층</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/joan_nail_l</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>1</v>
+      </c>
+      <c r="R151" t="n">
+        <v>4</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>1735186216</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1735186216</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>네일하오</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천매봉길 26-19 1층 네일하오</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>16</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>1482792466</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1482792466</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>희네일</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0507-1404-9740</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 봉바위길 74 1층 101호</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/heenail_s2</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>1366302200</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1366302200</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>네일문</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>abctnghcjstk@naver.com</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0507-1429-8120</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 중앙시장길 6 가동 1층 1-2호</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/abctnghcjstk</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>2</v>
+      </c>
+      <c r="R154" t="n">
+        <v>110</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>1863474701</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1863474701</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>네일해</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>qkrtjdal1349@naver.com</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 금불1길 64 1층</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailhae1349?igsh=ZWVmM2JscDVnZGJu</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>121</v>
+      </c>
+      <c r="R155" t="n">
+        <v>143</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>37870180</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37870180</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>혜이뷰티</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 북원상가길 17-2 2층</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hyei.beauty</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>139</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>1938200298</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1938200298</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>린지네일</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0507-1363-5022</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 중앙시장길 11 2층 40-2호</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>http://instagram.com/linzy5022</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>3</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>1261885827</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1261885827</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>윤꾸샵</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0507-1333-3991</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 백간공원길 20-1 윤꾸샵</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yunkku_</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>6</v>
+      </c>
+      <c r="R158" t="n">
+        <v>24</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>1709847911</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1709847911</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>DRAW NAIL studio</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>tkdqhd4247@naver.com</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0507-1321-5595</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천매봉길 34 1층</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tkdqhd4247</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>11</v>
+      </c>
+      <c r="R159" t="n">
+        <v>36</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>1125445323</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1125445323</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>낭그네일</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0507-1357-3817</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 이화1길 38-17 1층 낭그네일</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nangg_nail</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>78</v>
+      </c>
+      <c r="R160" t="n">
+        <v>156</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>1074138402</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1074138402</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>모모젤리</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0507-1478-0805</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 이화4길 3 1층</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>1</v>
+      </c>
+      <c r="R161" t="n">
+        <v>1</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>1343748315</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1343748315</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>코코샤네일</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0507-1318-5476</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 건강로 25 국민은행건물 6층</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>http://instagram.com/cococha_nail_</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>1</v>
+      </c>
+      <c r="R162" t="n">
+        <v>5</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>37933039</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37933039</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>네일정원</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0507-1359-5206</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 300 105호</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_garden_2</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>46</v>
+      </c>
+      <c r="R163" t="n">
+        <v>68</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>1996773507</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1996773507</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>단비네일</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>01031908662@naver.com</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>0507-1310-2206</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천매봉길 150-9 1층 단비네일</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/01031908662</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>107</v>
+      </c>
+      <c r="R164" t="n">
+        <v>113</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>1169405484</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1169405484</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>프롬윤네일 원주점</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0507-1378-5257</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 이화1길 41-12 1층 프롬윤네일</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xoIZHG/chat</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>222</v>
+      </c>
+      <c r="R165" t="n">
+        <v>443</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>1412889087</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1412889087</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>오후의네일</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>whitehousez@naver.com</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>0507-1479-0057</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 27 SK타워 5층 503호</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail_salon_of_owho</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>14</v>
+      </c>
+      <c r="R166" t="n">
+        <v>47</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>1648575759</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1648575759</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>네일,데이지</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>0507-1309-3129</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 325-2 이지더원1차아파트 상가동 2층 네일,데이지</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail._.daisy</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>2025117668</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2025117668</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>원주네일밸류</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>rlatndus9800@naver.com</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 408 602호</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailvalue_salon_official</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>31</v>
+      </c>
+      <c r="R168" t="n">
+        <v>234</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>1791919601</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1791919601</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>땡네일 원주본점</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>tjdud0505@naver.com</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>0507-1353-6255</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남원로469번길 2-23</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tjdud0505</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>90</v>
+      </c>
+      <c r="R169" t="n">
+        <v>227</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>1305168537</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1305168537</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>네일 스토리</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 치악고교길 25 1층</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>7</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>21398916</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21398916</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>달의네일</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>iamscalet@naver.com</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 무실로 157 109호</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_DDTNG</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>3</v>
+      </c>
+      <c r="R171" t="n">
+        <v>3</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>1708981858</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1708981858</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>유아나네일</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>unicef2000@naver.com</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0507-1438-7844</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로51번길 40 상가동 2층 유아나네일</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/youana__nail/</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>3</v>
+      </c>
+      <c r="R172" t="n">
+        <v>94</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>1751172620</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1751172620</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>나다운네일</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 봉바위길 1-1 101호</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nadaun_nail_</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>694</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>5</v>
+      </c>
+      <c r="R173" t="n">
+        <v>699</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>1265029601</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1265029601</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>진블리네일</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0507-1492-7945</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 북원로 2235-4 121호 1층 진블리네일</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_QLxbln/chat</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>423</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>41</v>
+      </c>
+      <c r="R174" t="n">
+        <v>464</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>1361153397</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1361153397</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>AURA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>aurayoga@naver.com</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 양지뜰4길 6 1층 1호 AURA</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wonju_aurabeauty</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>6</v>
+      </c>
+      <c r="R175" t="n">
+        <v>72</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>1731746293</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1731746293</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>유유네일</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>uunail@naver.com</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0507-1467-1440</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 88-1 상가동 2층 204호</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/uunail</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>18</v>
+      </c>
+      <c r="R176" t="n">
+        <v>164</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>1488329383</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1488329383</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>네일더끌림</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>rlduswlsl84@naver.com</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 나비허리길 107 1층 103호</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>http://instagram.com/thecclim_wj</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>5</v>
+      </c>
+      <c r="R177" t="n">
+        <v>11</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>1449071538</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1449071538</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>별네일 페디베네 원주점</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>pedibene_wonju@naver.com</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0507-1322-8233</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 원일로 233 축협하나로마트 2층</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pedibene_wonju</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>203</v>
+      </c>
+      <c r="R178" t="n">
+        <v>385</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>1975020913</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1975020913</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>네일봄</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>llo__ob@naver.com</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0507-1322-9731</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 만대공원길 50 107호 네일봄</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/llo__ob</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>105</v>
+      </c>
+      <c r="R179" t="n">
+        <v>310</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>1017730079</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1017730079</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>릿네일</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>jisuddong__@naver.com</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0507-1323-6281</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 121-1 M스타빌딩 1층 102호</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_litnail/</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>6</v>
+      </c>
+      <c r="R180" t="n">
+        <v>193</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>1102474018</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1102474018</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>네일화안스튜디오</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>seo961207@naver.com</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0507-1304-4760</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 관설안길 27-1 1층 101호</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_hwa.an</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>813</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>8</v>
+      </c>
+      <c r="R181" t="n">
+        <v>821</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>1434910874</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1434910874</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>글래드 네일 원주점</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0507-1310-0165</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 이화2길 23 1층 글래드네일 원주점</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glad_nail_studio</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>1026</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>14</v>
+      </c>
+      <c r="R182" t="n">
+        <v>1040</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>1333012511</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1333012511</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>예삐네일</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>hott0116@naver.com</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>0507-1386-8456</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 51 319호</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yeppi_nail</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>6</v>
+      </c>
+      <c r="R183" t="n">
+        <v>272</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>1771502408</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1771502408</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>솜솜네일</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>somsomnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0507-1331-7209</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 북원로 2235-4 타임시티 1층 123호</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/somsomnail</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>455</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>832</v>
+      </c>
+      <c r="R184" t="n">
+        <v>1287</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>1151701425</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1151701425</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>너의네일</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>555__555@naver.com</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 단구로 263 너의네일</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/your_nail___</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
+        <v>41</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>1566147901</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1566147901</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>도록네일앤래쉬</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0507-1345-4720</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 무실본동길 35 1층 도록네일</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dorok_nail</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>3</v>
+      </c>
+      <c r="R186" t="n">
+        <v>97</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>1326427844</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1326427844</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>아이도하</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>jinysexy27@naver.com</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0507-1422-8339</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 양지로 20 1층 121호</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/eyedoha_</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>1</v>
+      </c>
+      <c r="R187" t="n">
+        <v>35</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>2037018036</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2037018036</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>페블네일</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>sweeetbelle@naver.com</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>0507-1391-0623</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 나비허리길 57-2 1층 페블네일</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pebble.nail</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>3</v>
+      </c>
+      <c r="R188" t="n">
+        <v>130</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>1418754457</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1418754457</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>모브네일</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 조엄로 397 214동 102호</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_mauve</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>1</v>
+      </c>
+      <c r="R189" t="n">
+        <v>27</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>1982005714</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1982005714</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>네뜨네일</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>0507-1324-4958</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 가곡로 50-1 203호 네뜨네일</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nett_nail/</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>273</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>8</v>
+      </c>
+      <c r="R190" t="n">
+        <v>281</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>1391622141</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1391622141</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>보떼네일</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>suji_i@naver.com</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 500</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="n">
+        <v>1</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>1326515323</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1326515323</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>네일고백</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>0507-1332-0390</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 오리현길 62-2 상가119동 203호(반곡동, 반곡이편한 세상)</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>1</v>
+      </c>
+      <c r="R192" t="n">
+        <v>1</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>1532322462</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1532322462</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>묘미네일&amp;브로우</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>jinny408@naver.com</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>0507-1354-4916</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 단구초교길 6-26 1층</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>1693016714</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1693016714</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>진스네일</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>oslopark_yangsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 이화4길 22 1층</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>0</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>2068489054</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2068489054</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>골드문네일 변색변형 손톱발톱케어 물어뜯는손톱연장 발각질</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>moon066940@naver.com</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>0507-1306-6694</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 송림길 40-22 골드문네일</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gold_moon_nail</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>304</v>
+      </c>
+      <c r="R195" t="n">
+        <v>391</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>1027228643</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1027228643</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>네일제이</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>babastu@naver.com</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>0507-1471-2061</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 문막읍 왕건로 75 현진상가 2층 204호 네일제이</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/Nail.J_</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>0</v>
+      </c>
+      <c r="R196" t="n">
+        <v>4</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>1845687961</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1845687961</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>행복네일</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>0507-1439-0583</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 행구로 107 1층 행복네일</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/happy_nail_pedi_wonju</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>0</v>
+      </c>
+      <c r="R197" t="n">
+        <v>1</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>1594335605</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1594335605</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>네일,더봄</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>0507-1372-8464</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 이화1길 38 1층 네일,더봄</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailthebom_wonju</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>2</v>
+      </c>
+      <c r="R198" t="n">
+        <v>43</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>1397054474</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1397054474</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>네일뉴스</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>xeunax@naver.com</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 금불1길 6-5 1층 Nail News</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>266</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>23</v>
+      </c>
+      <c r="R199" t="n">
+        <v>289</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>1031113109</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1031113109</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>끌리네일</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>0507-1366-1056</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 건강로 25 서영에비뉴파크 111호</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_ccli_nail</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>12</v>
+      </c>
+      <c r="R200" t="n">
+        <v>123</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>1449756872</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1449756872</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>아이젤</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>bbangju0916@naver.com</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 원문로100번길 35 단계프라자107호 은성셀프세차장건너편</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bbangju0916</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>1</v>
+      </c>
+      <c r="R201" t="n">
+        <v>8</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>35076085</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35076085</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>밝은네일</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>minseon8580@naver.com</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 치악고교길 1-12 . 1층</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bright_nail_2337</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>5</v>
+      </c>
+      <c r="R202" t="n">
+        <v>121</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>1444516072</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1444516072</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>네일바이윤쓰</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>0507-1415-5047</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 능라동길 59 602-1호</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_by_yoons?igsh=NzU5M2E5bDg1emU5</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>2</v>
+      </c>
+      <c r="R203" t="n">
+        <v>52</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>1593647926</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1593647926</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>여리연네일</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>0507-1310-8214</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 반곡길 62 1층, 촘촘속눈썹, 여리연네일</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>0</v>
+      </c>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>2035786192</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2035786192</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>린네일</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>sini_97@naver.com</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>0507-1396-0418</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 황소마을길 41-13 1층</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rin_nail__0?igsh=c2xsd2xtNno5a21n&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>4</v>
+      </c>
+      <c r="R205" t="n">
+        <v>104</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>1162141346</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1162141346</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>레브네일</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>0507-1345-4141</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 판부면 오성마을길 63-16 102호</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>http://instagram.com/revenail_4666</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>20</v>
+      </c>
+      <c r="R206" t="n">
+        <v>39</v>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>1793816174</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1793816174</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>캔들네일</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>0507-1457-1520</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 만대로 196-10 2층</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/candle</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>0</v>
+      </c>
+      <c r="R207" t="n">
+        <v>45</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>2018121515</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2018121515</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>네일탐나</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 치악고교길 28 1층 네일탐나</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__.nail_tamna</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>1</v>
+      </c>
+      <c r="R208" t="n">
+        <v>99</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>1611111219</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1611111219</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>봄봄네일 단계점</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>jmg2616@naver.com</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 북원로 2235-12 3층 302호</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bomnail_studio?igsh=amZiMWYxNGZrbG84&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>2094098055</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2094098055</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>마말네일드</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천매봉길 118-25 1층 시은하다 에스테틱</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/marmal_nailde?igsh=ZThsZDNobjh4MnA4&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>10</v>
+      </c>
+      <c r="R210" t="n">
+        <v>14</v>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>1355454380</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1355454380</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>에일린뷰티</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>sss5117@naver.com</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 무실본동길 51-1 1층 에일린뷰티</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aileen_.beauty</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>5</v>
+      </c>
+      <c r="R211" t="n">
+        <v>19</v>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>1702021342</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1702021342</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>레모네일드</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>junyeong_han@naver.com</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 섬밭들1길 30 1층</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ExiyxmG</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>6</v>
+      </c>
+      <c r="R212" t="n">
+        <v>37</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>1993391843</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1993391843</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>미를담다</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>dididi836@naver.com</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>0507-1486-1063</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 판부면 오성마을길 47-20 명빌딩 1층</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dididi836</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>72</v>
+      </c>
+      <c r="R213" t="n">
+        <v>73</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>1396083735</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1396083735</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>손에핀꽃</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>flower7868@naver.com</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>0507-1420-1284</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남원로469번길 13 1층 102호</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>0</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>2060346099</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2060346099</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>화연네일</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>sujinkongjoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>0507-1388-4435</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 관설안길 19-3 1층 화연네일</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://instagram.com/hwa__nail</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>3</v>
+      </c>
+      <c r="R215" t="n">
+        <v>11</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>1389644064</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1389644064</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>앤느네일 원주점</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>algp91@naver.com</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>0507-1318-4058</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 한지공원길 11 1층</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xlfNmj</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>59</v>
+      </c>
+      <c r="R216" t="n">
+        <v>216</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>1480865518</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1480865518</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>오데뜨 네일</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>0507-1476-1022</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 조엄로 393 반도유보라1차 상가 2층 201호</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>http://instagram.com/odettewonju</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>169</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" t="n">
+        <v>169</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>1260481575</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1260481575</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>네일도</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>jisoo851208@naver.com</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>0507-1324-0238</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 황금로 5 B01, B02호</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nail.do_</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>17</v>
+      </c>
+      <c r="R218" t="n">
+        <v>64</v>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>1420375722</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1420375722</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>네일은그리다</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 구곡길 2-3</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>1572356890</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1572356890</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>네일리</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>0507-1343-4237</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 이화5길 34-1 1층</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_naily.___?igsh=dnB4MHRsZXI5dg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>92</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>2074922665</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2074922665</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>원멜리 네일앤뷰티</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>wonmeli_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>0507-1467-5661</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 이화4길 55 1층 101호</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wonmeli_nail</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>243</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>15</v>
+      </c>
+      <c r="R221" t="n">
+        <v>258</v>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>1804062627</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1804062627</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>블루시엘네일</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 문막읍 원문로 1700-1 2층 205호</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/blueciel_nail?igsh=Z2J3Mm1zZm5uZWk1</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>1</v>
+      </c>
+      <c r="R222" t="n">
+        <v>10</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>1341213457</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1341213457</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>네일그리</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>hongyummy@naver.com</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>0507-1351-9548</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 265 호반베르디움 단지내 상가 314동 203호</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://www.nailgree.com/</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>0</v>
+      </c>
+      <c r="R223" t="n">
+        <v>69</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>1419317959</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1419317959</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>진네일</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>0507-1346-2548</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 시청로 15-1 2층</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>18</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>1941855495</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1941855495</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>인투유네일</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0507-1364-5229</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 나비허리길 190 청솔8차 상가동 2층 203호</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_PlZtxj</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>18</v>
+      </c>
+      <c r="R225" t="n">
+        <v>59</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>1312759661</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1312759661</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>아롱별네일 단계점</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>arongstar_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>0507-1474-0548</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 서원대로 125-5 2층 아롱별네일(궁서채헤어샵 내부)</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/arongstar_nail</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>26</v>
+      </c>
+      <c r="R226" t="n">
+        <v>163</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>1940434767</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1940434767</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>네일한 나</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>0507-1376-4319</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 322 탑프라자 304호</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailhan_na_?igsh=MXV2ZWIyNThwZHg3bw==</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>3</v>
+      </c>
+      <c r="R227" t="n">
+        <v>250</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>1910389098</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1910389098</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>퀸네일</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>madam7333@naver.com</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>0507-1306-7334</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 지정면 신지정로 295 호반베르디움 상가동 329동 205</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/madam7333</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>5</v>
+      </c>
+      <c r="R228" t="n">
+        <v>254</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>1714997356</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1714997356</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>네일쉼터</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>0507-1467-7991</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 흥양로 94 네일쉼터</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rest._.nail/?igshid=NTdlMDg3MTY%3D</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>2</v>
+      </c>
+      <c r="R229" t="n">
+        <v>67</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>1858477262</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1858477262</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>별난손톱 더 푸스프로</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>0507-1444-1717</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 천매봉길 26-21 별난손톱</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sCJXRY4h</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>1</v>
+      </c>
+      <c r="R230" t="n">
+        <v>1</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>1309886515</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1309886515</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>네일바이윤</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>nail_by_youn@naver.com</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>0507-1397-5703</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 우러리길 16-3 1층</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_by_youn_</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>15</v>
+      </c>
+      <c r="R231" t="n">
+        <v>188</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>1156805140</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1156805140</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>나경네일</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 남산로48번길 31</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>0</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>1889383527</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1889383527</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>이뿐손네일</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 북원로 2700</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>0</v>
+      </c>
+      <c r="R233" t="n">
+        <v>2</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>898706712</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/898706712</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>안나뷰티</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 진광길 25 B동 1층 104호</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kimanna4586</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>4</v>
+      </c>
+      <c r="R234" t="n">
+        <v>13</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>1777477586</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1777477586</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>모나코헤어살롱</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>haha_owo@naver.com</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>033-763-0055</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>강원특별자치도 원주시 관설안길 3-39</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>1</v>
+      </c>
+      <c r="R235" t="n">
+        <v>13</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>21563173</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21563173</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
